--- a/BSE/FnO/bse_fno_consolidated.xlsx
+++ b/BSE/FnO/bse_fno_consolidated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1505"/>
+  <dimension ref="A1:O1506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78041,6 +78041,83 @@
         </is>
       </c>
     </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>1,15,58,823</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>2,86,40,184</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>47,80,688.88</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>11,226.86</t>
+        </is>
+      </c>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1506" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I1506" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="J1506" t="inlineStr">
+        <is>
+          <t>1,115</t>
+        </is>
+      </c>
+      <c r="K1506" t="inlineStr">
+        <is>
+          <t>186.35</t>
+        </is>
+      </c>
+      <c r="L1506" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M1506" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N1506" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="O1506" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/FnO/bse_fno_consolidated.xlsx
+++ b/BSE/FnO/bse_fno_consolidated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1506"/>
+  <dimension ref="A1:O1508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78118,6 +78118,160 @@
         </is>
       </c>
     </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>3,28,26,032</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>12,12,87,581</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>2,02,56,507.92</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>31,391.93</t>
+        </is>
+      </c>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1507" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I1507" t="inlineStr">
+        <is>
+          <t>1,107</t>
+        </is>
+      </c>
+      <c r="J1507" t="inlineStr">
+        <is>
+          <t>1,377</t>
+        </is>
+      </c>
+      <c r="K1507" t="inlineStr">
+        <is>
+          <t>230.41</t>
+        </is>
+      </c>
+      <c r="L1507" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M1507" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N1507" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="O1507" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>9,99,82,199</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>52,22,88,476</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>8,68,52,466.01</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>59,310.34</t>
+        </is>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>2,316</t>
+        </is>
+      </c>
+      <c r="J1508" t="inlineStr">
+        <is>
+          <t>2,827</t>
+        </is>
+      </c>
+      <c r="K1508" t="inlineStr">
+        <is>
+          <t>470.07</t>
+        </is>
+      </c>
+      <c r="L1508" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M1508" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N1508" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="O1508" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/FnO/bse_fno_consolidated.xlsx
+++ b/BSE/FnO/bse_fno_consolidated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1508"/>
+  <dimension ref="A1:O1509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78272,6 +78272,83 @@
         </is>
       </c>
     </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>20-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>1,06,67,721</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>2,36,51,608</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>39,34,473.34</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>14,746.16</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1509" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>1,842</t>
+        </is>
+      </c>
+      <c r="J1509" t="inlineStr">
+        <is>
+          <t>2,260</t>
+        </is>
+      </c>
+      <c r="K1509" t="inlineStr">
+        <is>
+          <t>375.22</t>
+        </is>
+      </c>
+      <c r="L1509" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M1509" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N1509" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="O1509" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/FnO/bse_fno_consolidated.xlsx
+++ b/BSE/FnO/bse_fno_consolidated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1509"/>
+  <dimension ref="A1:O1519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78349,6 +78349,776 @@
         </is>
       </c>
     </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>23-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>95,95,616</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>2,16,18,696</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>36,06,871.05</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>11,966.11</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>1,194</t>
+        </is>
+      </c>
+      <c r="J1510" t="inlineStr">
+        <is>
+          <t>1,558</t>
+        </is>
+      </c>
+      <c r="K1510" t="inlineStr">
+        <is>
+          <t>260.19</t>
+        </is>
+      </c>
+      <c r="L1510" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M1510" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N1510" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="O1510" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>24-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>1,18,64,238</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>2,87,21,854</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>47,58,213.87</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>12,640.20</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H1511" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="I1511" t="inlineStr">
+        <is>
+          <t>2,154</t>
+        </is>
+      </c>
+      <c r="J1511" t="inlineStr">
+        <is>
+          <t>2,854</t>
+        </is>
+      </c>
+      <c r="K1511" t="inlineStr">
+        <is>
+          <t>472.72</t>
+        </is>
+      </c>
+      <c r="L1511" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M1511" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N1511" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="O1511" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>25-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>3,88,95,875</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>14,16,78,803</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>2,34,45,941.81</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>41,017.67</t>
+        </is>
+      </c>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H1512" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="I1512" t="inlineStr">
+        <is>
+          <t>2,704</t>
+        </is>
+      </c>
+      <c r="J1512" t="inlineStr">
+        <is>
+          <t>3,520</t>
+        </is>
+      </c>
+      <c r="K1512" t="inlineStr">
+        <is>
+          <t>582.63</t>
+        </is>
+      </c>
+      <c r="L1512" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M1512" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N1512" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="O1512" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>10,15,57,091</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>54,03,60,343</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>8,92,21,796.07</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>65,720.73</t>
+        </is>
+      </c>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H1513" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="I1513" t="inlineStr">
+        <is>
+          <t>3,788</t>
+        </is>
+      </c>
+      <c r="J1513" t="inlineStr">
+        <is>
+          <t>4,886</t>
+        </is>
+      </c>
+      <c r="K1513" t="inlineStr">
+        <is>
+          <t>807.05</t>
+        </is>
+      </c>
+      <c r="L1513" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M1513" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N1513" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="O1513" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>27-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>88,46,655</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>2,05,79,844</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>33,74,119.67</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>12,283.41</t>
+        </is>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H1514" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="I1514" t="inlineStr">
+        <is>
+          <t>1,852</t>
+        </is>
+      </c>
+      <c r="J1514" t="inlineStr">
+        <is>
+          <t>2,141</t>
+        </is>
+      </c>
+      <c r="K1514" t="inlineStr">
+        <is>
+          <t>352.18</t>
+        </is>
+      </c>
+      <c r="L1514" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M1514" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N1514" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="O1514" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>02-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>1,45,03,223</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>3,12,35,653</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>50,25,429.76</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>17,949.10</t>
+        </is>
+      </c>
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H1515" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="I1515" t="inlineStr">
+        <is>
+          <t>2,427</t>
+        </is>
+      </c>
+      <c r="J1515" t="inlineStr">
+        <is>
+          <t>3,194</t>
+        </is>
+      </c>
+      <c r="K1515" t="inlineStr">
+        <is>
+          <t>514.62</t>
+        </is>
+      </c>
+      <c r="L1515" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M1515" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N1515" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="O1515" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>3,98,38,499</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>11,14,83,952</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>1,76,56,684.78</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>52,828.20</t>
+        </is>
+      </c>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H1516" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="I1516" t="inlineStr">
+        <is>
+          <t>2,990</t>
+        </is>
+      </c>
+      <c r="J1516" t="inlineStr">
+        <is>
+          <t>4,018</t>
+        </is>
+      </c>
+      <c r="K1516" t="inlineStr">
+        <is>
+          <t>637.52</t>
+        </is>
+      </c>
+      <c r="L1516" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M1516" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N1516" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="O1516" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>05-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>13,07,41,416</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>62,59,00,100</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>9,96,48,985.22</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>82,816.90</t>
+        </is>
+      </c>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H1517" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="I1517" t="inlineStr">
+        <is>
+          <t>3,099</t>
+        </is>
+      </c>
+      <c r="J1517" t="inlineStr">
+        <is>
+          <t>4,280</t>
+        </is>
+      </c>
+      <c r="K1517" t="inlineStr">
+        <is>
+          <t>684.78</t>
+        </is>
+      </c>
+      <c r="L1517" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M1517" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N1517" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="O1517" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>06-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>74,01,246</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>1,47,03,915</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>23,53,771.32</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>13,521.95</t>
+        </is>
+      </c>
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H1518" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="I1518" t="inlineStr">
+        <is>
+          <t>1,573</t>
+        </is>
+      </c>
+      <c r="J1518" t="inlineStr">
+        <is>
+          <t>2,009</t>
+        </is>
+      </c>
+      <c r="K1518" t="inlineStr">
+        <is>
+          <t>320.42</t>
+        </is>
+      </c>
+      <c r="L1518" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M1518" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N1518" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="O1518" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>09-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>81,41,807</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>1,56,91,652</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>24,61,220.41</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>16,419.64</t>
+        </is>
+      </c>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H1519" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="I1519" t="inlineStr">
+        <is>
+          <t>2,366</t>
+        </is>
+      </c>
+      <c r="J1519" t="inlineStr">
+        <is>
+          <t>3,377</t>
+        </is>
+      </c>
+      <c r="K1519" t="inlineStr">
+        <is>
+          <t>522.91</t>
+        </is>
+      </c>
+      <c r="L1519" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M1519" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N1519" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="O1519" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/FnO/bse_fno_consolidated.xlsx
+++ b/BSE/FnO/bse_fno_consolidated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1519"/>
+  <dimension ref="A1:O1521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79119,6 +79119,160 @@
         </is>
       </c>
     </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>10-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>1,02,01,973</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>2,27,10,548</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>35,58,885.92</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>12,706.07</t>
+        </is>
+      </c>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="I1520" t="inlineStr">
+        <is>
+          <t>1,536</t>
+        </is>
+      </c>
+      <c r="J1520" t="inlineStr">
+        <is>
+          <t>1,979</t>
+        </is>
+      </c>
+      <c r="K1520" t="inlineStr">
+        <is>
+          <t>310.74</t>
+        </is>
+      </c>
+      <c r="L1520" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M1520" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N1520" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="O1520" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>3,84,39,934</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>11,63,67,477</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>1,80,49,273.56</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>48,035.77</t>
+        </is>
+      </c>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H1521" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="I1521" t="inlineStr">
+        <is>
+          <t>2,625</t>
+        </is>
+      </c>
+      <c r="J1521" t="inlineStr">
+        <is>
+          <t>3,405</t>
+        </is>
+      </c>
+      <c r="K1521" t="inlineStr">
+        <is>
+          <t>529.78</t>
+        </is>
+      </c>
+      <c r="L1521" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M1521" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N1521" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="O1521" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/FnO/bse_fno_consolidated.xlsx
+++ b/BSE/FnO/bse_fno_consolidated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1521"/>
+  <dimension ref="A1:O1533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79273,6 +79273,930 @@
         </is>
       </c>
     </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>12,33,78,416</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>56,27,28,553</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>8,60,52,859.00</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>77,891.18</t>
+        </is>
+      </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="I1522" t="inlineStr">
+        <is>
+          <t>3,056</t>
+        </is>
+      </c>
+      <c r="J1522" t="inlineStr">
+        <is>
+          <t>4,039</t>
+        </is>
+      </c>
+      <c r="K1522" t="inlineStr">
+        <is>
+          <t>619.19</t>
+        </is>
+      </c>
+      <c r="L1522" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M1522" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N1522" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="O1522" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>13-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>64,49,280</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>1,24,86,343</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>18,97,037.85</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>13,204.79</t>
+        </is>
+      </c>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H1523" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="I1523" t="inlineStr">
+        <is>
+          <t>2,963</t>
+        </is>
+      </c>
+      <c r="J1523" t="inlineStr">
+        <is>
+          <t>3,744</t>
+        </is>
+      </c>
+      <c r="K1523" t="inlineStr">
+        <is>
+          <t>564.83</t>
+        </is>
+      </c>
+      <c r="L1523" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M1523" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N1523" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="O1523" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>16-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>1,06,76,003</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>2,19,43,551</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>33,16,490.87</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>17,971.38</t>
+        </is>
+      </c>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H1524" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="I1524" t="inlineStr">
+        <is>
+          <t>3,041</t>
+        </is>
+      </c>
+      <c r="J1524" t="inlineStr">
+        <is>
+          <t>3,948</t>
+        </is>
+      </c>
+      <c r="K1524" t="inlineStr">
+        <is>
+          <t>593.72</t>
+        </is>
+      </c>
+      <c r="L1524" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M1524" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N1524" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="O1524" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>1,35,46,882</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>2,97,76,518</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>45,05,085.33</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>15,473.09</t>
+        </is>
+      </c>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I1525" t="inlineStr">
+        <is>
+          <t>2,306</t>
+        </is>
+      </c>
+      <c r="J1525" t="inlineStr">
+        <is>
+          <t>2,931</t>
+        </is>
+      </c>
+      <c r="K1525" t="inlineStr">
+        <is>
+          <t>445.64</t>
+        </is>
+      </c>
+      <c r="L1525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M1525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N1525" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="O1525" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>18-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>3,47,65,545</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>11,71,92,146</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>1,79,59,225.26</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>42,367.33</t>
+        </is>
+      </c>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H1526" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="I1526" t="inlineStr">
+        <is>
+          <t>2,697</t>
+        </is>
+      </c>
+      <c r="J1526" t="inlineStr">
+        <is>
+          <t>3,370</t>
+        </is>
+      </c>
+      <c r="K1526" t="inlineStr">
+        <is>
+          <t>518.21</t>
+        </is>
+      </c>
+      <c r="L1526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M1526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N1526" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="O1526" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>19-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>10,62,57,473</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>51,12,37,978</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>7,65,40,874.55</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>69,373.46</t>
+        </is>
+      </c>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H1527" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="I1527" t="inlineStr">
+        <is>
+          <t>4,662</t>
+        </is>
+      </c>
+      <c r="J1527" t="inlineStr">
+        <is>
+          <t>5,973</t>
+        </is>
+      </c>
+      <c r="K1527" t="inlineStr">
+        <is>
+          <t>896.49</t>
+        </is>
+      </c>
+      <c r="L1527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M1527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N1527" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="O1527" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>20-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>82,12,225</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>1,59,24,022</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>24,06,659.79</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>15,001.51</t>
+        </is>
+      </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H1528" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="I1528" t="inlineStr">
+        <is>
+          <t>2,848</t>
+        </is>
+      </c>
+      <c r="J1528" t="inlineStr">
+        <is>
+          <t>3,511</t>
+        </is>
+      </c>
+      <c r="K1528" t="inlineStr">
+        <is>
+          <t>527.40</t>
+        </is>
+      </c>
+      <c r="L1528" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M1528" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N1528" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="O1528" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>23-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>86,66,757</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>1,70,31,961</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>25,07,615.46</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>15,618.10</t>
+        </is>
+      </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H1529" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="I1529" t="inlineStr">
+        <is>
+          <t>3,250</t>
+        </is>
+      </c>
+      <c r="J1529" t="inlineStr">
+        <is>
+          <t>4,084</t>
+        </is>
+      </c>
+      <c r="K1529" t="inlineStr">
+        <is>
+          <t>597.26</t>
+        </is>
+      </c>
+      <c r="L1529" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M1529" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N1529" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="O1529" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>24-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>1,87,06,122</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>4,18,00,283</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>61,90,609.22</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>21,587.61</t>
+        </is>
+      </c>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H1530" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="I1530" t="inlineStr">
+        <is>
+          <t>4,147</t>
+        </is>
+      </c>
+      <c r="J1530" t="inlineStr">
+        <is>
+          <t>5,420</t>
+        </is>
+      </c>
+      <c r="K1530" t="inlineStr">
+        <is>
+          <t>803.71</t>
+        </is>
+      </c>
+      <c r="L1530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M1530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N1530" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="O1530" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>10,62,71,264</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>48,75,42,044</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>7,36,57,415.18</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>72,196.20</t>
+        </is>
+      </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H1531" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="I1531" t="inlineStr">
+        <is>
+          <t>6,856</t>
+        </is>
+      </c>
+      <c r="J1531" t="inlineStr">
+        <is>
+          <t>8,751</t>
+        </is>
+      </c>
+      <c r="K1531" t="inlineStr">
+        <is>
+          <t>1,323.78</t>
+        </is>
+      </c>
+      <c r="L1531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M1531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N1531" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="O1531" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>27-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>45,15,614</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>86,73,449</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>12,97,523.18</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>10,052.94</t>
+        </is>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H1532" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="I1532" t="inlineStr">
+        <is>
+          <t>3,425</t>
+        </is>
+      </c>
+      <c r="J1532" t="inlineStr">
+        <is>
+          <t>12,602</t>
+        </is>
+      </c>
+      <c r="K1532" t="inlineStr">
+        <is>
+          <t>1,873.77</t>
+        </is>
+      </c>
+      <c r="L1532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M1532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N1532" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="O1532" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>30-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>80,66,557</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>1,62,17,500</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>23,75,865.31</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>12,787.76</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="I1533" t="inlineStr">
+        <is>
+          <t>3,244</t>
+        </is>
+      </c>
+      <c r="J1533" t="inlineStr">
+        <is>
+          <t>16,879</t>
+        </is>
+      </c>
+      <c r="K1533" t="inlineStr">
+        <is>
+          <t>2,469.52</t>
+        </is>
+      </c>
+      <c r="L1533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M1533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N1533" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="O1533" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/FnO/bse_fno_consolidated.xlsx
+++ b/BSE/FnO/bse_fno_consolidated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1533"/>
+  <dimension ref="A1:O1537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80197,6 +80197,314 @@
         </is>
       </c>
     </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>3,57,20,293</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>10,45,05,127</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>1,53,86,265.00</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>43,456.73</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H1534" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="I1534" t="inlineStr">
+        <is>
+          <t>2,836</t>
+        </is>
+      </c>
+      <c r="J1534" t="inlineStr">
+        <is>
+          <t>6,755</t>
+        </is>
+      </c>
+      <c r="K1534" t="inlineStr">
+        <is>
+          <t>999.04</t>
+        </is>
+      </c>
+      <c r="L1534" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M1534" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N1534" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="O1534" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>02-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>12,84,68,663</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>60,10,67,981</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>8,72,88,918.15</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>85,211.35</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H1535" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="I1535" t="inlineStr">
+        <is>
+          <t>3,459</t>
+        </is>
+      </c>
+      <c r="J1535" t="inlineStr">
+        <is>
+          <t>10,833</t>
+        </is>
+      </c>
+      <c r="K1535" t="inlineStr">
+        <is>
+          <t>1,594.58</t>
+        </is>
+      </c>
+      <c r="L1535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M1535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N1535" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O1535" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>06-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>90,91,187</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>2,08,58,331</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>30,92,454.30</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>16,337.04</t>
+        </is>
+      </c>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="I1536" t="inlineStr">
+        <is>
+          <t>1,879</t>
+        </is>
+      </c>
+      <c r="J1536" t="inlineStr">
+        <is>
+          <t>2,382</t>
+        </is>
+      </c>
+      <c r="K1536" t="inlineStr">
+        <is>
+          <t>352.09</t>
+        </is>
+      </c>
+      <c r="L1536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M1536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N1536" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="O1536" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>07-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>87,58,820</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>2,10,78,837</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>31,20,225.43</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>14,206.35</t>
+        </is>
+      </c>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H1537" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I1537" t="inlineStr">
+        <is>
+          <t>1,653</t>
+        </is>
+      </c>
+      <c r="J1537" t="inlineStr">
+        <is>
+          <t>2,108</t>
+        </is>
+      </c>
+      <c r="K1537" t="inlineStr">
+        <is>
+          <t>314.19</t>
+        </is>
+      </c>
+      <c r="L1537" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M1537" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N1537" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="O1537" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
